--- a/49K14.2_Group08_TestReport_MNS.xlsx
+++ b/49K14.2_Group08_TestReport_MNS.xlsx
@@ -1,68 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lqdvk\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\updatetl\GROUP-PROJECT_FINAL-REPORT_49K14.2_08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E869F62-263A-4265-8414-4B28C3ED84A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8EB4AA-9E0C-4F6A-82E2-2824DED287B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Test report sprint 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Test report" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
-  <si>
-    <t>Project Name</t>
-  </si>
-  <si>
-    <t>Test Environment Setup Description</t>
-  </si>
-  <si>
-    <t>Staging — Deployed on Vercel / Render</t>
-  </si>
-  <si>
-    <t>Tester</t>
-  </si>
-  <si>
-    <t>Pham Thuy Duong</t>
-  </si>
-  <si>
-    <t>Hà Gia Bảo Ngọc</t>
-  </si>
-  <si>
-    <t>Phan Nhật Minh Anh</t>
-  </si>
-  <si>
-    <t>Đặng Thị Thanh Ngân</t>
-  </si>
-  <si>
-    <t>Lê Thị Thanh Nhàn</t>
-  </si>
-  <si>
-    <t>Đặng Ngọc Anh Thư</t>
-  </si>
-  <si>
-    <t>Test Result</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>SKIPPED</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>No</t>
   </si>
@@ -156,15 +119,12 @@
   <si>
     <t>Login - Test</t>
   </si>
-  <si>
-    <t>Hệ thống quản lý cửa hàng tạp hóa</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,20 +141,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="163"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="163"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
@@ -217,7 +163,7 @@
       <charset val="163"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,18 +172,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF95B3D7"/>
-        <bgColor rgb="FF95B3D7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF8DB3E2"/>
         <bgColor rgb="FF8DB3E2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -271,43 +211,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -373,36 +276,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -411,29 +301,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -649,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA1001"/>
+  <dimension ref="A1:AA985"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="22.09765625" customWidth="1"/>
@@ -661,52 +541,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="2"/>
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
     </row>
     <row r="2" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="10">
+        <v>46134</v>
+      </c>
+      <c r="F2" s="9">
+        <v>16</v>
+      </c>
+      <c r="G2" s="9">
+        <v>13</v>
+      </c>
+      <c r="H2" s="9">
         <v>0</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="I2" s="11">
+        <v>3</v>
+      </c>
+      <c r="J2" s="10">
+        <v>46141</v>
+      </c>
+      <c r="K2" s="12">
+        <v>13</v>
+      </c>
+      <c r="L2" s="9">
+        <v>0</v>
+      </c>
+      <c r="M2" s="9">
+        <v>3</v>
+      </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -717,29 +645,51 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
-      <c r="X2" s="2"/>
+      <c r="X2" s="1"/>
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
     </row>
-    <row r="3" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="22" t="s">
+    <row r="3" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="B3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="10">
+        <v>46136</v>
+      </c>
+      <c r="F3" s="13">
+        <v>6</v>
+      </c>
+      <c r="G3" s="13">
+        <v>3</v>
+      </c>
+      <c r="H3" s="13">
+        <v>3</v>
+      </c>
+      <c r="I3" s="13">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10">
+        <v>46141</v>
+      </c>
+      <c r="K3" s="9">
+        <v>6</v>
+      </c>
+      <c r="L3" s="9">
+        <v>0</v>
+      </c>
+      <c r="M3" s="13">
+        <v>0</v>
+      </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
@@ -750,25 +700,51 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
-      <c r="X3" s="2"/>
+      <c r="X3" s="1"/>
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
       <c r="AA3" s="2"/>
     </row>
-    <row r="4" spans="1:27" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+    <row r="4" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="10">
+        <v>46137</v>
+      </c>
+      <c r="F4" s="13">
+        <v>59</v>
+      </c>
+      <c r="G4" s="13">
+        <v>50</v>
+      </c>
+      <c r="H4" s="13">
+        <v>9</v>
+      </c>
+      <c r="I4" s="13">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10">
+        <v>46143</v>
+      </c>
+      <c r="K4" s="9">
+        <v>50</v>
+      </c>
+      <c r="L4" s="9">
+        <v>9</v>
+      </c>
+      <c r="M4" s="13">
+        <v>0</v>
+      </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -779,29 +755,51 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
-      <c r="X4" s="2"/>
+      <c r="X4" s="1"/>
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
     </row>
-    <row r="5" spans="1:27" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+    <row r="5" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="10">
+        <v>46141</v>
+      </c>
+      <c r="F5" s="13">
+        <v>20</v>
+      </c>
+      <c r="G5" s="13">
+        <v>15</v>
+      </c>
+      <c r="H5" s="13">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="I5" s="13">
+        <v>2</v>
+      </c>
+      <c r="J5" s="10">
+        <v>46142</v>
+      </c>
+      <c r="K5" s="13">
+        <v>15</v>
+      </c>
+      <c r="L5" s="13">
+        <v>2</v>
+      </c>
+      <c r="M5" s="13">
+        <v>3</v>
+      </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -812,27 +810,51 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
-      <c r="X5" s="2"/>
+      <c r="X5" s="1"/>
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
     </row>
-    <row r="6" spans="1:27" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="24"/>
-      <c r="B6" s="6" t="s">
+    <row r="6" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="B6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="10">
+        <v>46138</v>
+      </c>
+      <c r="F6" s="13">
+        <v>35</v>
+      </c>
+      <c r="G6" s="13">
+        <v>20</v>
+      </c>
+      <c r="H6" s="13">
+        <v>15</v>
+      </c>
+      <c r="I6" s="13">
+        <v>0</v>
+      </c>
+      <c r="J6" s="10">
+        <v>46141</v>
+      </c>
+      <c r="K6" s="9">
+        <v>35</v>
+      </c>
+      <c r="L6" s="9">
+        <v>0</v>
+      </c>
+      <c r="M6" s="13">
+        <v>0</v>
+      </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -843,27 +865,51 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
     </row>
-    <row r="7" spans="1:27" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
-      <c r="B7" s="6" t="s">
+    <row r="7" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="B7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="10">
+        <v>46135</v>
+      </c>
+      <c r="F7" s="13">
+        <v>7</v>
+      </c>
+      <c r="G7" s="13">
+        <v>2</v>
+      </c>
+      <c r="H7" s="13">
+        <v>5</v>
+      </c>
+      <c r="I7" s="13">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10">
+        <v>46143</v>
+      </c>
+      <c r="K7" s="9">
+        <v>5</v>
+      </c>
+      <c r="L7" s="9">
+        <v>2</v>
+      </c>
+      <c r="M7" s="13">
+        <v>0</v>
+      </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -874,17 +920,15 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2"/>
-    </row>
-    <row r="8" spans="1:27" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="24"/>
-      <c r="B8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+    </row>
+    <row r="8" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -905,17 +949,15 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
-    </row>
-    <row r="9" spans="1:27" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+    </row>
+    <row r="9" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -936,17 +978,15 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
-    </row>
-    <row r="10" spans="1:27" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="24"/>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="2"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+    </row>
+    <row r="10" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="14"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -967,15 +1007,15 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
-    </row>
-    <row r="11" spans="1:27" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+    </row>
+    <row r="11" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="2"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -996,19 +1036,15 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
-    </row>
-    <row r="12" spans="1:27" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="2"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+    </row>
+    <row r="12" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -1034,12 +1070,10 @@
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
     </row>
-    <row r="13" spans="1:27" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="24"/>
-      <c r="B13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="2"/>
+    <row r="13" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -1065,12 +1099,10 @@
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
     </row>
-    <row r="14" spans="1:27" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="25"/>
-      <c r="B14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="2"/>
+    <row r="14" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -1099,7 +1131,7 @@
     <row r="15" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="2"/>
+      <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -1127,7 +1159,7 @@
     </row>
     <row r="16" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
+      <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1155,100 +1187,48 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="L17" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M17" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="2"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14">
-        <v>1</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="15">
-        <v>46134</v>
-      </c>
-      <c r="F18" s="14">
-        <v>17</v>
-      </c>
-      <c r="G18" s="14">
-        <v>14</v>
-      </c>
-      <c r="H18" s="14">
-        <v>0</v>
-      </c>
-      <c r="I18" s="16">
-        <v>3</v>
-      </c>
-      <c r="J18" s="15">
-        <v>46141</v>
-      </c>
-      <c r="K18" s="17">
-        <v>14</v>
-      </c>
-      <c r="L18" s="14">
-        <v>0</v>
-      </c>
-      <c r="M18" s="14">
-        <v>3</v>
-      </c>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
@@ -1260,50 +1240,24 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
-      <c r="Y18" s="2"/>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="2"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14">
-        <v>2</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="15">
-        <v>46137</v>
-      </c>
-      <c r="F19" s="18">
-        <v>6</v>
-      </c>
-      <c r="G19" s="18">
-        <v>3</v>
-      </c>
-      <c r="H19" s="18">
-        <v>3</v>
-      </c>
-      <c r="I19" s="18">
-        <v>0</v>
-      </c>
-      <c r="J19" s="15">
-        <v>46141</v>
-      </c>
-      <c r="K19" s="14">
-        <v>6</v>
-      </c>
-      <c r="L19" s="14">
-        <v>0</v>
-      </c>
-      <c r="M19" s="18">
-        <v>0</v>
-      </c>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
@@ -1315,50 +1269,24 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14">
-        <v>3</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="15">
-        <v>46137</v>
-      </c>
-      <c r="F20" s="18">
-        <v>59</v>
-      </c>
-      <c r="G20" s="18">
-        <v>50</v>
-      </c>
-      <c r="H20" s="18">
-        <v>9</v>
-      </c>
-      <c r="I20" s="18">
-        <v>0</v>
-      </c>
-      <c r="J20" s="15">
-        <v>46143</v>
-      </c>
-      <c r="K20" s="14">
-        <v>50</v>
-      </c>
-      <c r="L20" s="14">
-        <v>9</v>
-      </c>
-      <c r="M20" s="18">
-        <v>0</v>
-      </c>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
@@ -1370,50 +1298,24 @@
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="2"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14">
-        <v>4</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" s="15">
-        <v>46138</v>
-      </c>
-      <c r="F21" s="18">
-        <v>20</v>
-      </c>
-      <c r="G21" s="18">
-        <v>15</v>
-      </c>
-      <c r="H21" s="18">
-        <v>3</v>
-      </c>
-      <c r="I21" s="18">
-        <v>2</v>
-      </c>
-      <c r="J21" s="15">
-        <v>46142</v>
-      </c>
-      <c r="K21" s="18">
-        <v>15</v>
-      </c>
-      <c r="L21" s="18">
-        <v>3</v>
-      </c>
-      <c r="M21" s="18">
-        <v>2</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
@@ -1425,50 +1327,24 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14">
-        <v>5</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="15">
-        <v>46138</v>
-      </c>
-      <c r="F22" s="18">
-        <v>35</v>
-      </c>
-      <c r="G22" s="18">
-        <v>20</v>
-      </c>
-      <c r="H22" s="18">
-        <v>15</v>
-      </c>
-      <c r="I22" s="18">
-        <v>0</v>
-      </c>
-      <c r="J22" s="15">
-        <v>46141</v>
-      </c>
-      <c r="K22" s="14">
-        <v>35</v>
-      </c>
-      <c r="L22" s="14">
-        <v>0</v>
-      </c>
-      <c r="M22" s="18">
-        <v>0</v>
-      </c>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -1481,49 +1357,23 @@
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="2"/>
+      <c r="Z22" s="1"/>
+      <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="14">
-        <v>6</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="15">
-        <v>46137</v>
-      </c>
-      <c r="F23" s="18">
-        <v>7</v>
-      </c>
-      <c r="G23" s="18">
-        <v>2</v>
-      </c>
-      <c r="H23" s="18">
-        <v>5</v>
-      </c>
-      <c r="I23" s="18">
-        <v>0</v>
-      </c>
-      <c r="J23" s="15">
-        <v>46143</v>
-      </c>
-      <c r="K23" s="14">
-        <v>5</v>
-      </c>
-      <c r="L23" s="14">
-        <v>2</v>
-      </c>
-      <c r="M23" s="18">
-        <v>0</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -1572,7 +1422,6 @@
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -1598,7 +1447,7 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="19"/>
+      <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -2036,6 +1885,7 @@
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -6618,11 +6468,11 @@
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
-      <c r="E199" s="1"/>
-      <c r="F199" s="1"/>
-      <c r="G199" s="1"/>
-      <c r="H199" s="1"/>
-      <c r="I199" s="1"/>
+      <c r="E199" s="2"/>
+      <c r="F199" s="2"/>
+      <c r="G199" s="2"/>
+      <c r="H199" s="2"/>
+      <c r="I199" s="2"/>
       <c r="J199" s="1"/>
       <c r="K199" s="1"/>
       <c r="L199" s="1"/>
@@ -6647,11 +6497,11 @@
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
-      <c r="E200" s="1"/>
-      <c r="F200" s="1"/>
-      <c r="G200" s="1"/>
-      <c r="H200" s="1"/>
-      <c r="I200" s="1"/>
+      <c r="E200" s="2"/>
+      <c r="F200" s="2"/>
+      <c r="G200" s="2"/>
+      <c r="H200" s="2"/>
+      <c r="I200" s="2"/>
       <c r="J200" s="1"/>
       <c r="K200" s="1"/>
       <c r="L200" s="1"/>
@@ -6676,11 +6526,11 @@
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
-      <c r="E201" s="1"/>
-      <c r="F201" s="1"/>
-      <c r="G201" s="1"/>
-      <c r="H201" s="1"/>
-      <c r="I201" s="1"/>
+      <c r="E201" s="2"/>
+      <c r="F201" s="2"/>
+      <c r="G201" s="2"/>
+      <c r="H201" s="2"/>
+      <c r="I201" s="2"/>
       <c r="J201" s="1"/>
       <c r="K201" s="1"/>
       <c r="L201" s="1"/>
@@ -6705,11 +6555,6 @@
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
-      <c r="E202" s="1"/>
-      <c r="F202" s="1"/>
-      <c r="G202" s="1"/>
-      <c r="H202" s="1"/>
-      <c r="I202" s="1"/>
       <c r="J202" s="1"/>
       <c r="K202" s="1"/>
       <c r="L202" s="1"/>
@@ -6734,11 +6579,6 @@
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
-      <c r="E203" s="1"/>
-      <c r="F203" s="1"/>
-      <c r="G203" s="1"/>
-      <c r="H203" s="1"/>
-      <c r="I203" s="1"/>
       <c r="J203" s="1"/>
       <c r="K203" s="1"/>
       <c r="L203" s="1"/>
@@ -6763,11 +6603,6 @@
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
-      <c r="E204" s="1"/>
-      <c r="F204" s="1"/>
-      <c r="G204" s="1"/>
-      <c r="H204" s="1"/>
-      <c r="I204" s="1"/>
       <c r="J204" s="1"/>
       <c r="K204" s="1"/>
       <c r="L204" s="1"/>
@@ -6787,528 +6622,95 @@
       <c r="Z204" s="1"/>
       <c r="AA204" s="1"/>
     </row>
-    <row r="205" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="1"/>
-      <c r="B205" s="1"/>
-      <c r="C205" s="1"/>
-      <c r="D205" s="1"/>
-      <c r="E205" s="1"/>
-      <c r="F205" s="1"/>
-      <c r="G205" s="1"/>
-      <c r="H205" s="1"/>
-      <c r="I205" s="1"/>
-      <c r="J205" s="1"/>
-      <c r="K205" s="1"/>
-      <c r="L205" s="1"/>
-      <c r="M205" s="1"/>
-      <c r="N205" s="1"/>
-      <c r="O205" s="1"/>
-      <c r="P205" s="1"/>
-      <c r="Q205" s="1"/>
-      <c r="R205" s="1"/>
-      <c r="S205" s="1"/>
-      <c r="T205" s="1"/>
-      <c r="U205" s="1"/>
-      <c r="V205" s="1"/>
-      <c r="W205" s="1"/>
-      <c r="X205" s="1"/>
-      <c r="Y205" s="1"/>
-      <c r="Z205" s="1"/>
-      <c r="AA205" s="1"/>
-    </row>
-    <row r="206" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="1"/>
-      <c r="B206" s="1"/>
-      <c r="C206" s="1"/>
-      <c r="D206" s="1"/>
-      <c r="E206" s="1"/>
-      <c r="F206" s="1"/>
-      <c r="G206" s="1"/>
-      <c r="H206" s="1"/>
-      <c r="I206" s="1"/>
-      <c r="J206" s="1"/>
-      <c r="K206" s="1"/>
-      <c r="L206" s="1"/>
-      <c r="M206" s="1"/>
-      <c r="N206" s="1"/>
-      <c r="O206" s="1"/>
-      <c r="P206" s="1"/>
-      <c r="Q206" s="1"/>
-      <c r="R206" s="1"/>
-      <c r="S206" s="1"/>
-      <c r="T206" s="1"/>
-      <c r="U206" s="1"/>
-      <c r="V206" s="1"/>
-      <c r="W206" s="1"/>
-      <c r="X206" s="1"/>
-      <c r="Y206" s="1"/>
-      <c r="Z206" s="1"/>
-      <c r="AA206" s="1"/>
-    </row>
-    <row r="207" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="1"/>
-      <c r="B207" s="1"/>
-      <c r="C207" s="1"/>
-      <c r="D207" s="1"/>
-      <c r="E207" s="1"/>
-      <c r="F207" s="1"/>
-      <c r="G207" s="1"/>
-      <c r="H207" s="1"/>
-      <c r="I207" s="1"/>
-      <c r="J207" s="1"/>
-      <c r="K207" s="1"/>
-      <c r="L207" s="1"/>
-      <c r="M207" s="1"/>
-      <c r="N207" s="1"/>
-      <c r="O207" s="1"/>
-      <c r="P207" s="1"/>
-      <c r="Q207" s="1"/>
-      <c r="R207" s="1"/>
-      <c r="S207" s="1"/>
-      <c r="T207" s="1"/>
-      <c r="U207" s="1"/>
-      <c r="V207" s="1"/>
-      <c r="W207" s="1"/>
-      <c r="X207" s="1"/>
-      <c r="Y207" s="1"/>
-      <c r="Z207" s="1"/>
-      <c r="AA207" s="1"/>
-    </row>
-    <row r="208" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="1"/>
-      <c r="B208" s="1"/>
-      <c r="C208" s="1"/>
-      <c r="D208" s="1"/>
-      <c r="E208" s="1"/>
-      <c r="F208" s="1"/>
-      <c r="G208" s="1"/>
-      <c r="H208" s="1"/>
-      <c r="I208" s="1"/>
-      <c r="J208" s="1"/>
-      <c r="K208" s="1"/>
-      <c r="L208" s="1"/>
-      <c r="M208" s="1"/>
-      <c r="N208" s="1"/>
-      <c r="O208" s="1"/>
-      <c r="P208" s="1"/>
-      <c r="Q208" s="1"/>
-      <c r="R208" s="1"/>
-      <c r="S208" s="1"/>
-      <c r="T208" s="1"/>
-      <c r="U208" s="1"/>
-      <c r="V208" s="1"/>
-      <c r="W208" s="1"/>
-      <c r="X208" s="1"/>
-      <c r="Y208" s="1"/>
-      <c r="Z208" s="1"/>
-      <c r="AA208" s="1"/>
-    </row>
-    <row r="209" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="1"/>
-      <c r="B209" s="1"/>
-      <c r="C209" s="1"/>
-      <c r="D209" s="1"/>
-      <c r="E209" s="1"/>
-      <c r="F209" s="1"/>
-      <c r="G209" s="1"/>
-      <c r="H209" s="1"/>
-      <c r="I209" s="1"/>
-      <c r="J209" s="1"/>
-      <c r="K209" s="1"/>
-      <c r="L209" s="1"/>
-      <c r="M209" s="1"/>
-      <c r="N209" s="1"/>
-      <c r="O209" s="1"/>
-      <c r="P209" s="1"/>
-      <c r="Q209" s="1"/>
-      <c r="R209" s="1"/>
-      <c r="S209" s="1"/>
-      <c r="T209" s="1"/>
-      <c r="U209" s="1"/>
-      <c r="V209" s="1"/>
-      <c r="W209" s="1"/>
-      <c r="X209" s="1"/>
-      <c r="Y209" s="1"/>
-      <c r="Z209" s="1"/>
-      <c r="AA209" s="1"/>
-    </row>
-    <row r="210" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="1"/>
-      <c r="B210" s="1"/>
-      <c r="C210" s="1"/>
-      <c r="D210" s="1"/>
-      <c r="E210" s="1"/>
-      <c r="F210" s="1"/>
-      <c r="G210" s="1"/>
-      <c r="H210" s="1"/>
-      <c r="I210" s="1"/>
-      <c r="J210" s="1"/>
-      <c r="K210" s="1"/>
-      <c r="L210" s="1"/>
-      <c r="M210" s="1"/>
-      <c r="N210" s="1"/>
-      <c r="O210" s="1"/>
-      <c r="P210" s="1"/>
-      <c r="Q210" s="1"/>
-      <c r="R210" s="1"/>
-      <c r="S210" s="1"/>
-      <c r="T210" s="1"/>
-      <c r="U210" s="1"/>
-      <c r="V210" s="1"/>
-      <c r="W210" s="1"/>
-      <c r="X210" s="1"/>
-      <c r="Y210" s="1"/>
-      <c r="Z210" s="1"/>
-      <c r="AA210" s="1"/>
-    </row>
-    <row r="211" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="1"/>
-      <c r="B211" s="1"/>
-      <c r="C211" s="1"/>
-      <c r="D211" s="1"/>
-      <c r="E211" s="1"/>
-      <c r="F211" s="1"/>
-      <c r="G211" s="1"/>
-      <c r="H211" s="1"/>
-      <c r="I211" s="1"/>
-      <c r="J211" s="1"/>
-      <c r="K211" s="1"/>
-      <c r="L211" s="1"/>
-      <c r="M211" s="1"/>
-      <c r="N211" s="1"/>
-      <c r="O211" s="1"/>
-      <c r="P211" s="1"/>
-      <c r="Q211" s="1"/>
-      <c r="R211" s="1"/>
-      <c r="S211" s="1"/>
-      <c r="T211" s="1"/>
-      <c r="U211" s="1"/>
-      <c r="V211" s="1"/>
-      <c r="W211" s="1"/>
-      <c r="X211" s="1"/>
-      <c r="Y211" s="1"/>
-      <c r="Z211" s="1"/>
-      <c r="AA211" s="1"/>
-    </row>
-    <row r="212" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="1"/>
-      <c r="B212" s="1"/>
-      <c r="C212" s="1"/>
-      <c r="D212" s="1"/>
-      <c r="E212" s="1"/>
-      <c r="F212" s="1"/>
-      <c r="G212" s="1"/>
-      <c r="H212" s="1"/>
-      <c r="I212" s="1"/>
-      <c r="J212" s="1"/>
-      <c r="K212" s="1"/>
-      <c r="L212" s="1"/>
-      <c r="M212" s="1"/>
-      <c r="N212" s="1"/>
-      <c r="O212" s="1"/>
-      <c r="P212" s="1"/>
-      <c r="Q212" s="1"/>
-      <c r="R212" s="1"/>
-      <c r="S212" s="1"/>
-      <c r="T212" s="1"/>
-      <c r="U212" s="1"/>
-      <c r="V212" s="1"/>
-      <c r="W212" s="1"/>
-      <c r="X212" s="1"/>
-      <c r="Y212" s="1"/>
-      <c r="Z212" s="1"/>
-      <c r="AA212" s="1"/>
-    </row>
-    <row r="213" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="1"/>
-      <c r="B213" s="1"/>
-      <c r="C213" s="1"/>
-      <c r="D213" s="1"/>
-      <c r="E213" s="1"/>
-      <c r="F213" s="1"/>
-      <c r="G213" s="1"/>
-      <c r="H213" s="1"/>
-      <c r="I213" s="1"/>
-      <c r="J213" s="1"/>
-      <c r="K213" s="1"/>
-      <c r="L213" s="1"/>
-      <c r="M213" s="1"/>
-      <c r="N213" s="1"/>
-      <c r="O213" s="1"/>
-      <c r="P213" s="1"/>
-      <c r="Q213" s="1"/>
-      <c r="R213" s="1"/>
-      <c r="S213" s="1"/>
-      <c r="T213" s="1"/>
-      <c r="U213" s="1"/>
-      <c r="V213" s="1"/>
-      <c r="W213" s="1"/>
-      <c r="X213" s="1"/>
-      <c r="Y213" s="1"/>
-      <c r="Z213" s="1"/>
-      <c r="AA213" s="1"/>
-    </row>
-    <row r="214" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="1"/>
-      <c r="B214" s="1"/>
-      <c r="C214" s="1"/>
-      <c r="D214" s="1"/>
-      <c r="E214" s="1"/>
-      <c r="F214" s="1"/>
-      <c r="G214" s="1"/>
-      <c r="H214" s="1"/>
-      <c r="I214" s="1"/>
-      <c r="J214" s="1"/>
-      <c r="K214" s="1"/>
-      <c r="L214" s="1"/>
-      <c r="M214" s="1"/>
-      <c r="N214" s="1"/>
-      <c r="O214" s="1"/>
-      <c r="P214" s="1"/>
-      <c r="Q214" s="1"/>
-      <c r="R214" s="1"/>
-      <c r="S214" s="1"/>
-      <c r="T214" s="1"/>
-      <c r="U214" s="1"/>
-      <c r="V214" s="1"/>
-      <c r="W214" s="1"/>
-      <c r="X214" s="1"/>
-      <c r="Y214" s="1"/>
-      <c r="Z214" s="1"/>
-      <c r="AA214" s="1"/>
-    </row>
-    <row r="215" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="1"/>
-      <c r="B215" s="1"/>
-      <c r="C215" s="1"/>
-      <c r="D215" s="1"/>
-      <c r="E215" s="2"/>
-      <c r="F215" s="2"/>
-      <c r="G215" s="2"/>
-      <c r="H215" s="2"/>
-      <c r="I215" s="2"/>
-      <c r="J215" s="1"/>
-      <c r="K215" s="1"/>
-      <c r="L215" s="1"/>
-      <c r="M215" s="1"/>
-      <c r="N215" s="1"/>
-      <c r="O215" s="1"/>
-      <c r="P215" s="1"/>
-      <c r="Q215" s="1"/>
-      <c r="R215" s="1"/>
-      <c r="S215" s="1"/>
-      <c r="T215" s="1"/>
-      <c r="U215" s="1"/>
-      <c r="V215" s="1"/>
-      <c r="W215" s="1"/>
-      <c r="X215" s="1"/>
-      <c r="Y215" s="1"/>
-      <c r="Z215" s="1"/>
-      <c r="AA215" s="1"/>
-    </row>
-    <row r="216" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="1"/>
-      <c r="B216" s="1"/>
-      <c r="C216" s="1"/>
-      <c r="D216" s="1"/>
-      <c r="E216" s="2"/>
-      <c r="F216" s="2"/>
-      <c r="G216" s="2"/>
-      <c r="H216" s="2"/>
-      <c r="I216" s="2"/>
-      <c r="J216" s="1"/>
-      <c r="K216" s="1"/>
-      <c r="L216" s="1"/>
-      <c r="M216" s="1"/>
-      <c r="N216" s="1"/>
-      <c r="O216" s="1"/>
-      <c r="P216" s="1"/>
-      <c r="Q216" s="1"/>
-      <c r="R216" s="1"/>
-      <c r="S216" s="1"/>
-      <c r="T216" s="1"/>
-      <c r="U216" s="1"/>
-      <c r="V216" s="1"/>
-      <c r="W216" s="1"/>
-      <c r="X216" s="1"/>
-      <c r="Y216" s="1"/>
-      <c r="Z216" s="1"/>
-      <c r="AA216" s="1"/>
-    </row>
-    <row r="217" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="1"/>
-      <c r="B217" s="1"/>
-      <c r="C217" s="1"/>
-      <c r="D217" s="1"/>
-      <c r="E217" s="2"/>
-      <c r="F217" s="2"/>
-      <c r="G217" s="2"/>
-      <c r="H217" s="2"/>
-      <c r="I217" s="2"/>
-      <c r="J217" s="1"/>
-      <c r="K217" s="1"/>
-      <c r="L217" s="1"/>
-      <c r="M217" s="1"/>
-      <c r="N217" s="1"/>
-      <c r="O217" s="1"/>
-      <c r="P217" s="1"/>
-      <c r="Q217" s="1"/>
-      <c r="R217" s="1"/>
-      <c r="S217" s="1"/>
-      <c r="T217" s="1"/>
-      <c r="U217" s="1"/>
-      <c r="V217" s="1"/>
-      <c r="W217" s="1"/>
-      <c r="X217" s="1"/>
-      <c r="Y217" s="1"/>
-      <c r="Z217" s="1"/>
-      <c r="AA217" s="1"/>
-    </row>
-    <row r="218" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="1"/>
-      <c r="B218" s="1"/>
-      <c r="C218" s="1"/>
-      <c r="D218" s="1"/>
-      <c r="J218" s="1"/>
-      <c r="K218" s="1"/>
-      <c r="L218" s="1"/>
-      <c r="M218" s="1"/>
-      <c r="N218" s="1"/>
-      <c r="O218" s="1"/>
-      <c r="P218" s="1"/>
-      <c r="Q218" s="1"/>
-      <c r="R218" s="1"/>
-      <c r="S218" s="1"/>
-      <c r="T218" s="1"/>
-      <c r="U218" s="1"/>
-      <c r="V218" s="1"/>
-      <c r="W218" s="1"/>
-      <c r="X218" s="1"/>
-      <c r="Y218" s="1"/>
-      <c r="Z218" s="1"/>
-      <c r="AA218" s="1"/>
-    </row>
-    <row r="219" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="1"/>
-      <c r="B219" s="1"/>
-      <c r="C219" s="1"/>
-      <c r="D219" s="1"/>
-      <c r="J219" s="1"/>
-      <c r="K219" s="1"/>
-      <c r="L219" s="1"/>
-      <c r="M219" s="1"/>
-      <c r="N219" s="1"/>
-      <c r="O219" s="1"/>
-      <c r="P219" s="1"/>
-      <c r="Q219" s="1"/>
-      <c r="R219" s="1"/>
-      <c r="S219" s="1"/>
-      <c r="T219" s="1"/>
-      <c r="U219" s="1"/>
-      <c r="V219" s="1"/>
-      <c r="W219" s="1"/>
-      <c r="X219" s="1"/>
-      <c r="Y219" s="1"/>
-      <c r="Z219" s="1"/>
-      <c r="AA219" s="1"/>
-    </row>
-    <row r="220" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="1"/>
-      <c r="B220" s="1"/>
-      <c r="C220" s="1"/>
-      <c r="D220" s="1"/>
-      <c r="J220" s="1"/>
-      <c r="K220" s="1"/>
-      <c r="L220" s="1"/>
-      <c r="M220" s="1"/>
-      <c r="N220" s="1"/>
-      <c r="O220" s="1"/>
-      <c r="P220" s="1"/>
-      <c r="Q220" s="1"/>
-      <c r="R220" s="1"/>
-      <c r="S220" s="1"/>
-      <c r="T220" s="1"/>
-      <c r="U220" s="1"/>
-      <c r="V220" s="1"/>
-      <c r="W220" s="1"/>
-      <c r="X220" s="1"/>
-      <c r="Y220" s="1"/>
-      <c r="Z220" s="1"/>
-      <c r="AA220" s="1"/>
-    </row>
-    <row r="221" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="2"/>
-      <c r="B221" s="2"/>
-      <c r="C221" s="2"/>
-      <c r="D221" s="2"/>
-      <c r="J221" s="2"/>
-      <c r="K221" s="2"/>
-      <c r="L221" s="2"/>
-      <c r="M221" s="2"/>
-      <c r="N221" s="2"/>
-      <c r="O221" s="2"/>
-      <c r="P221" s="2"/>
-      <c r="Q221" s="2"/>
-      <c r="R221" s="2"/>
-      <c r="S221" s="2"/>
-      <c r="T221" s="2"/>
-      <c r="U221" s="2"/>
-      <c r="V221" s="2"/>
-      <c r="W221" s="2"/>
-      <c r="X221" s="2"/>
-      <c r="Y221" s="2"/>
-      <c r="Z221" s="2"/>
-      <c r="AA221" s="2"/>
-    </row>
-    <row r="222" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="2"/>
-      <c r="B222" s="2"/>
-      <c r="C222" s="2"/>
-      <c r="D222" s="2"/>
-      <c r="J222" s="2"/>
-      <c r="K222" s="2"/>
-      <c r="L222" s="2"/>
-      <c r="M222" s="2"/>
-      <c r="N222" s="2"/>
-      <c r="O222" s="2"/>
-      <c r="P222" s="2"/>
-      <c r="Q222" s="2"/>
-      <c r="R222" s="2"/>
-      <c r="S222" s="2"/>
-      <c r="T222" s="2"/>
-      <c r="U222" s="2"/>
-      <c r="V222" s="2"/>
-      <c r="W222" s="2"/>
-      <c r="X222" s="2"/>
-      <c r="Y222" s="2"/>
-      <c r="Z222" s="2"/>
-      <c r="AA222" s="2"/>
-    </row>
-    <row r="223" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="2"/>
-      <c r="B223" s="2"/>
-      <c r="C223" s="2"/>
-      <c r="D223" s="2"/>
-      <c r="J223" s="2"/>
-      <c r="K223" s="2"/>
-      <c r="L223" s="2"/>
-      <c r="M223" s="2"/>
-      <c r="N223" s="2"/>
-      <c r="O223" s="2"/>
-      <c r="P223" s="2"/>
-      <c r="Q223" s="2"/>
-      <c r="R223" s="2"/>
-      <c r="S223" s="2"/>
-      <c r="T223" s="2"/>
-      <c r="U223" s="2"/>
-      <c r="V223" s="2"/>
-      <c r="W223" s="2"/>
-      <c r="X223" s="2"/>
-      <c r="Y223" s="2"/>
-      <c r="Z223" s="2"/>
-      <c r="AA223" s="2"/>
-    </row>
-    <row r="224" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="2"/>
+      <c r="B205" s="2"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
+      <c r="J205" s="2"/>
+      <c r="K205" s="2"/>
+      <c r="L205" s="2"/>
+      <c r="M205" s="2"/>
+      <c r="N205" s="2"/>
+      <c r="O205" s="2"/>
+      <c r="P205" s="2"/>
+      <c r="Q205" s="2"/>
+      <c r="R205" s="2"/>
+      <c r="S205" s="2"/>
+      <c r="T205" s="2"/>
+      <c r="U205" s="2"/>
+      <c r="V205" s="2"/>
+      <c r="W205" s="2"/>
+      <c r="X205" s="2"/>
+      <c r="Y205" s="2"/>
+      <c r="Z205" s="2"/>
+      <c r="AA205" s="2"/>
+    </row>
+    <row r="206" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="2"/>
+      <c r="B206" s="2"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="2"/>
+      <c r="J206" s="2"/>
+      <c r="K206" s="2"/>
+      <c r="L206" s="2"/>
+      <c r="M206" s="2"/>
+      <c r="N206" s="2"/>
+      <c r="O206" s="2"/>
+      <c r="P206" s="2"/>
+      <c r="Q206" s="2"/>
+      <c r="R206" s="2"/>
+      <c r="S206" s="2"/>
+      <c r="T206" s="2"/>
+      <c r="U206" s="2"/>
+      <c r="V206" s="2"/>
+      <c r="W206" s="2"/>
+      <c r="X206" s="2"/>
+      <c r="Y206" s="2"/>
+      <c r="Z206" s="2"/>
+      <c r="AA206" s="2"/>
+    </row>
+    <row r="207" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="2"/>
+      <c r="B207" s="2"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
+      <c r="J207" s="2"/>
+      <c r="K207" s="2"/>
+      <c r="L207" s="2"/>
+      <c r="M207" s="2"/>
+      <c r="N207" s="2"/>
+      <c r="O207" s="2"/>
+      <c r="P207" s="2"/>
+      <c r="Q207" s="2"/>
+      <c r="R207" s="2"/>
+      <c r="S207" s="2"/>
+      <c r="T207" s="2"/>
+      <c r="U207" s="2"/>
+      <c r="V207" s="2"/>
+      <c r="W207" s="2"/>
+      <c r="X207" s="2"/>
+      <c r="Y207" s="2"/>
+      <c r="Z207" s="2"/>
+      <c r="AA207" s="2"/>
+    </row>
+    <row r="208" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8070,29 +7472,7 @@
     <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A5:A10"/>
-    <mergeCell ref="A12:A14"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
